--- a/Data/t13.1.xlsx
+++ b/Data/t13.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,11 +463,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78.36935839482931</v>
+        <v>77.92623641290558</v>
       </c>
     </row>
     <row r="3">
@@ -483,11 +483,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79.11397427123318</v>
+        <v>78.77513300197317</v>
       </c>
     </row>
     <row r="4">
@@ -503,11 +503,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79.72812284384679</v>
+        <v>79.42807608577873</v>
       </c>
     </row>
     <row r="5">
@@ -523,11 +523,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80.23577424471007</v>
+        <v>79.9873550081463</v>
       </c>
     </row>
     <row r="6">
@@ -543,11 +543,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.73708333931381</v>
+        <v>80.49850199333471</v>
       </c>
     </row>
     <row r="7">
@@ -563,11 +563,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81.261256991184</v>
+        <v>80.98455414619281</v>
       </c>
     </row>
     <row r="8">
@@ -583,11 +583,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81.83249814315128</v>
+        <v>81.53830905881576</v>
       </c>
     </row>
     <row r="9">
@@ -598,16 +598,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45.51490501263478</v>
+        <v>82.14841042357482</v>
       </c>
     </row>
     <row r="10">
@@ -623,11 +623,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45.40373533291675</v>
+        <v>45.32482162974089</v>
       </c>
     </row>
     <row r="11">
@@ -643,11 +643,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43.63099869346291</v>
+        <v>45.74418662736968</v>
       </c>
     </row>
     <row r="12">
@@ -663,11 +663,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44.80581022010754</v>
+        <v>44.24234364687688</v>
       </c>
     </row>
     <row r="13">
@@ -683,11 +683,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41.97968547410927</v>
+        <v>43.87423096563967</v>
       </c>
     </row>
     <row r="14">
@@ -703,11 +703,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.99393307422505</v>
+        <v>39.72723294364321</v>
       </c>
     </row>
     <row r="15">
@@ -723,11 +723,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48.09755272040089</v>
+        <v>45.92094236849122</v>
       </c>
     </row>
     <row r="16">
@@ -738,16 +738,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.693785299358697</v>
+        <v>47.14086142286745</v>
       </c>
     </row>
     <row r="17">
@@ -758,16 +758,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.169766219339225</v>
+        <v>48.266640439124</v>
       </c>
     </row>
     <row r="18">
@@ -783,11 +783,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.569385927567932</v>
+        <v>3.714059534562726</v>
       </c>
     </row>
     <row r="19">
@@ -803,11 +803,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.187865072917875</v>
+        <v>3.397357444363963</v>
       </c>
     </row>
     <row r="20">
@@ -823,11 +823,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.971815150253811</v>
+        <v>5.704955820207453</v>
       </c>
     </row>
     <row r="21">
@@ -843,11 +843,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.013650582993648</v>
+        <v>6.297205943146171</v>
       </c>
     </row>
     <row r="22">
@@ -863,11 +863,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.939462030969416</v>
+        <v>6.241614288530991</v>
       </c>
     </row>
     <row r="23">
@@ -878,16 +878,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.16117146049996</v>
+        <v>4.711366320039614</v>
       </c>
     </row>
     <row r="24">
@@ -898,16 +898,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.54096864740481</v>
+        <v>3.486846452270603</v>
       </c>
     </row>
     <row r="25">
@@ -918,16 +918,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.52822756254985</v>
+        <v>2.744993349444538</v>
       </c>
     </row>
     <row r="26">
@@ -943,11 +943,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.24209895168465</v>
+        <v>28.88735524860196</v>
       </c>
     </row>
     <row r="27">
@@ -963,11 +963,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.78558271495075</v>
+        <v>29.63358893023953</v>
       </c>
     </row>
     <row r="28">
@@ -983,11 +983,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31.25414731254147</v>
+        <v>29.48126914703941</v>
       </c>
     </row>
     <row r="29">
@@ -1003,11 +1003,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.79548339178098</v>
+        <v>29.81591809936046</v>
       </c>
     </row>
     <row r="30">
@@ -1018,16 +1018,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>49.20818693432935</v>
+        <v>34.52965476116051</v>
       </c>
     </row>
     <row r="31">
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>49.57300562382837</v>
+        <v>30.35224545766198</v>
       </c>
     </row>
     <row r="32">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>50.20038462103085</v>
+        <v>30.91012922286933</v>
       </c>
     </row>
     <row r="33">
@@ -1078,16 +1078,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50.994158833314</v>
+        <v>31.13630828603008</v>
       </c>
     </row>
     <row r="34">
@@ -1103,11 +1103,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48.95150062436308</v>
+        <v>49.03888116430362</v>
       </c>
     </row>
     <row r="35">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>50.00710967864252</v>
+        <v>49.14104453380623</v>
       </c>
     </row>
     <row r="36">
@@ -1143,111 +1143,111 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>51.0370147513703</v>
+        <v>49.94680693873932</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>75.96452246726774</v>
+        <v>50.17143690878584</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>76.96066854391862</v>
+        <v>45.96884723217421</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>78.04030951952493</v>
+        <v>50.63230868853083</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>78.6671663900341</v>
+        <v>50.62817983594642</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>51.01210213754472</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>79.97745724802311</v>
+        <v>75.47333616565381</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80.88755737762359</v>
+        <v>76.44953341003306</v>
       </c>
     </row>
     <row r="44">
@@ -1298,16 +1298,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>39.00875920450998</v>
+        <v>77.35194157205871</v>
       </c>
     </row>
     <row r="45">
@@ -1318,16 +1318,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>40.19075302025615</v>
+        <v>78.42782396788991</v>
       </c>
     </row>
     <row r="46">
@@ -1338,16 +1338,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>36.60968148281447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1358,16 +1358,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>37.50602345130375</v>
+        <v>79.66544786533129</v>
       </c>
     </row>
     <row r="48">
@@ -1378,16 +1378,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>80.42538991147956</v>
       </c>
     </row>
     <row r="49">
@@ -1398,16 +1398,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>37.94931403110196</v>
+        <v>81.16314437044417</v>
       </c>
     </row>
     <row r="50">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>40.44290269455833</v>
+        <v>39.40742929973955</v>
       </c>
     </row>
     <row r="51">
@@ -1438,16 +1438,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.388783811080302</v>
+        <v>40.38788144414617</v>
       </c>
     </row>
     <row r="52">
@@ -1458,16 +1458,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.645290217095104</v>
+        <v>38.25475450141008</v>
       </c>
     </row>
     <row r="53">
@@ -1478,16 +1478,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.947993521684362</v>
+        <v>36.65961869266055</v>
       </c>
     </row>
     <row r="54">
@@ -1498,16 +1498,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.501757955417537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1518,16 +1518,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>38.11138784378146</v>
       </c>
     </row>
     <row r="56">
@@ -1538,16 +1538,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.851975132526726</v>
+        <v>39.25284529998595</v>
       </c>
     </row>
     <row r="57">
@@ -1558,16 +1558,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.628368197904622</v>
+        <v>40.64013145244463</v>
       </c>
     </row>
     <row r="58">
@@ -1578,16 +1578,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32.56697945167747</v>
+        <v>4.246633540831594</v>
       </c>
     </row>
     <row r="59">
@@ -1598,16 +1598,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32.12462530656735</v>
+        <v>3.918990485582278</v>
       </c>
     </row>
     <row r="60">
@@ -1618,16 +1618,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>34.48263451502609</v>
+        <v>5.906066960734687</v>
       </c>
     </row>
     <row r="61">
@@ -1638,16 +1638,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>34.66116970962503</v>
+        <v>6.470398509174312</v>
       </c>
     </row>
     <row r="62">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1678,16 +1678,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>37.17616808439443</v>
+        <v>5.553494780350802</v>
       </c>
     </row>
     <row r="64">
@@ -1698,16 +1698,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>36.81628648516066</v>
+        <v>4.088801461289869</v>
       </c>
     </row>
     <row r="65">
@@ -1718,16 +1718,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>43.39754301559029</v>
+        <v>3.34224832625378</v>
       </c>
     </row>
     <row r="66">
@@ -1738,16 +1738,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>44.83604323735126</v>
+        <v>31.81927332508266</v>
       </c>
     </row>
     <row r="67">
@@ -1758,16 +1758,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>43.55767500449883</v>
+        <v>32.14083529648094</v>
       </c>
     </row>
     <row r="68">
@@ -1778,16 +1778,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>44.00778140672128</v>
+        <v>33.19112010991395</v>
       </c>
     </row>
     <row r="69">
@@ -1798,16 +1798,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>35.29601490825688</v>
       </c>
     </row>
     <row r="70">
@@ -1818,16 +1818,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>42.80128916362868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1838,216 +1838,216 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>44.07127089246294</v>
+        <v>36.00056524119902</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>76.63246268656717</v>
+        <v>37.08374315020374</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>77.69619091326297</v>
+        <v>37.18076459174576</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>78.46153846153847</v>
+        <v>43.65406284057114</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>78.76620473848904</v>
+        <v>44.30869811355211</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>44.16082146214477</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>78.52760736196319</v>
+        <v>43.13180905963303</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>79.82608695652173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>41.18470149253731</v>
+        <v>43.66488262413227</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>42.4506654428637</v>
+        <v>43.34164676127582</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>38.55203619909503</v>
+        <v>43.98237977869841</v>
       </c>
     </row>
     <row r="82">
@@ -2058,16 +2058,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>40.32185963343764</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="83">
@@ -2078,16 +2078,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>76.22571692876966</v>
       </c>
     </row>
     <row r="84">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>39.83347940403155</v>
+        <v>78.0865603644647</v>
       </c>
     </row>
     <row r="85">
@@ -2118,16 +2118,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>41.21739130434783</v>
+        <v>77.51798561151078</v>
       </c>
     </row>
     <row r="86">
@@ -2138,16 +2138,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5.270522388059701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2158,16 +2158,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4.313905461220743</v>
+        <v>79.35739436619718</v>
       </c>
     </row>
     <row r="88">
@@ -2178,16 +2178,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.425339366515836</v>
+        <v>80.09602793539939</v>
       </c>
     </row>
     <row r="89">
@@ -2198,16 +2198,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7.375949932945909</v>
+        <v>80.63258232235701</v>
       </c>
     </row>
     <row r="90">
@@ -2218,16 +2218,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>40.04705882352941</v>
       </c>
     </row>
     <row r="91">
@@ -2238,16 +2238,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4.601226993865031</v>
+        <v>41.0268270120259</v>
       </c>
     </row>
     <row r="92">
@@ -2258,16 +2258,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3.608695652173913</v>
+        <v>39.95444191343964</v>
       </c>
     </row>
     <row r="93">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30.17723880597015</v>
+        <v>37.0953237410072</v>
       </c>
     </row>
     <row r="94">
@@ -2298,16 +2298,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30.9775126204681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2318,16 +2318,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>33.43891402714932</v>
+        <v>40.49295774647887</v>
       </c>
     </row>
     <row r="96">
@@ -2338,16 +2338,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>31.0683951721055</v>
+        <v>42.51418594500218</v>
       </c>
     </row>
     <row r="97">
@@ -2358,16 +2358,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade ocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>42.20103986135182</v>
       </c>
     </row>
     <row r="98">
@@ -2378,16 +2378,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2012</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>34.09290096406661</v>
+        <v>4.941176470588235</v>
       </c>
     </row>
     <row r="99">
@@ -2398,16 +2398,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2014</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>35.04347826086956</v>
+        <v>4.440333024976873</v>
       </c>
     </row>
     <row r="100">
@@ -2418,16 +2418,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>01/04/2013</t>
+          <t>01/04/2016</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>46.50186567164179</v>
+        <v>5.922551252847381</v>
       </c>
     </row>
     <row r="101">
@@ -2438,16 +2438,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>01/04/2018</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>46.76457090408444</v>
+        <v>7.643884892086331</v>
       </c>
     </row>
     <row r="102">
@@ -2458,16 +2458,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>45.02262443438914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2478,16 +2478,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>47.74251229324989</v>
+        <v>5.985915492957746</v>
       </c>
     </row>
     <row r="104">
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>4.321257092972501</v>
       </c>
     </row>
     <row r="105">
@@ -2518,16 +2518,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+          <t>Pessoas de 14 anos ou mais de idade, desocupadas na semana de referência</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>44.3908851884312</v>
+        <v>3.639514731369151</v>
       </c>
     </row>
     <row r="106">
@@ -2538,16 +2538,316 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01/04/2012</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>30.25882352941177</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>01/04/2014</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>30.71230342275671</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01/04/2016</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>32.16400911161731</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>01/04/2018</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>32.77877697841727</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>01/04/2020</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>01/04/2022</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>32.87852112676056</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>33.26058489742471</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, fora da força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>34.83535528596187</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>01/04/2025</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>44.82608695652173</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>01/04/2012</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>44.94117647058823</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>01/04/2014</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>45.46716003700277</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>01/04/2016</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>45.87699316628701</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>01/04/2018</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>44.73920863309353</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>01/04/2020</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>01/04/2022</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>46.47887323943662</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>46.83544303797468</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>45.79722703639515</v>
       </c>
     </row>
   </sheetData>
